--- a/data/trans_orig/IQ17B_M_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Edad-trans_orig.xlsx
@@ -721,42 +721,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,91</t>
+          <t>2,15; 2,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,29</t>
+          <t>2,22; 3,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 6,59</t>
+          <t>3,96; 6,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,22</t>
+          <t>2,24; 3,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,92</t>
+          <t>1,97; 2,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,45</t>
+          <t>2,25; 3,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,47</t>
+          <t>2,86; 4,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,85</t>
+          <t>2,21; 2,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 3,14</t>
+          <t>2,35; 3,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,21</t>
+          <t>3,62; 5,11</t>
         </is>
       </c>
     </row>
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,99</t>
+          <t>4,56; 5,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 6,27</t>
+          <t>4,03; 6,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,71</t>
+          <t>4,42; 5,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 9,22</t>
+          <t>6,34; 9,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,68</t>
+          <t>4,45; 5,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 5,68</t>
+          <t>4,36; 5,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 6,15</t>
+          <t>4,9; 6,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,81</t>
+          <t>7,07; 9,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 5,57</t>
+          <t>4,69; 5,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,59</t>
+          <t>4,36; 5,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 8,95</t>
+          <t>6,93; 8,79</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,0</t>
+          <t>7,07; 10,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,53</t>
+          <t>5,05; 6,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,77</t>
+          <t>6,51; 8,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 10,55</t>
+          <t>7,09; 11,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 9,93</t>
+          <t>6,94; 9,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 7,96</t>
+          <t>5,98; 7,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,33</t>
+          <t>5,92; 8,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 10,9</t>
+          <t>7,99; 11,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 9,54</t>
+          <t>7,27; 9,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 6,97</t>
+          <t>5,77; 7,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,04</t>
+          <t>6,45; 8,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 9,93</t>
+          <t>7,85; 9,98</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,29</t>
+          <t>7,4; 10,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 8,03</t>
+          <t>6,17; 8,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,06</t>
+          <t>7,06; 9,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,26</t>
+          <t>8,2; 10,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,11</t>
+          <t>7,68; 10,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 10,83</t>
+          <t>7,41; 11,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,7</t>
+          <t>8,01; 10,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,74</t>
+          <t>9,32; 15,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 9,74</t>
+          <t>7,77; 9,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,05</t>
+          <t>7,07; 9,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 9,81</t>
+          <t>7,86; 9,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,43</t>
+          <t>9,15; 12,46</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,06</t>
+          <t>5,83; 7,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,67</t>
+          <t>4,81; 5,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,65</t>
+          <t>5,62; 6,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,98</t>
+          <t>7,55; 8,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 6,88</t>
+          <t>5,8; 6,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,63</t>
+          <t>5,42; 6,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,97</t>
+          <t>5,9; 6,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,4</t>
+          <t>8,48; 11,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 6,85</t>
+          <t>5,95; 6,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,05</t>
+          <t>5,22; 5,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 6,67</t>
+          <t>5,91; 6,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 9,71</t>
+          <t>8,21; 9,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Edad-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función del número de meses de su última consulta al médico (tasa de respuesta: 91,3%)</t>
+          <t>Tiempo medio en meses desde la última consulta médica por algo que le pasaba a su hijo/a (tasa de respuesta: 91,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,75</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,71</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,67</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>5,24</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>4,52</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,88</t>
+          <t>2,22; 3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,88</t>
+          <t>1,99; 2,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,24</t>
+          <t>2,25; 3,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,61</t>
+          <t>3,03; 4,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,19</t>
+          <t>2,05; 2,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,85</t>
+          <t>2,18; 2,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,41</t>
+          <t>2,23; 3,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,49</t>
+          <t>4,12; 7,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,85</t>
+          <t>2,24; 2,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,7</t>
+          <t>2,17; 2,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,15</t>
+          <t>2,39; 3,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,11</t>
+          <t>3,83; 5,51</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,97</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8,47</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,67</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,04</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,4</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,5</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,19</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,8</t>
+          <t>8,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,9</t>
+          <t>4,45; 5,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,22</t>
+          <t>4,36; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,65</t>
+          <t>4,88; 6,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 9,15</t>
+          <t>7,33; 10,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 5,62</t>
+          <t>4,57; 5,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 5,73</t>
+          <t>4,05; 6,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,08</t>
+          <t>4,41; 5,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,88</t>
+          <t>6,68; 9,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 5,61</t>
+          <t>4,64; 5,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 5,56</t>
+          <t>4,37; 5,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,73</t>
+          <t>4,91; 5,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,79</t>
+          <t>7,31; 9,31</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,06</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,78</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,93</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,52</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,73</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,38</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,93</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,92</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,73</t>
+          <t>6,96; 9,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,57</t>
+          <t>5,99; 8,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,47</t>
+          <t>5,93; 8,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,15</t>
+          <t>8,23; 11,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,96</t>
+          <t>7,13; 11,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 7,98</t>
+          <t>5,06; 6,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,27</t>
+          <t>6,46; 8,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,09</t>
+          <t>7,2; 10,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,55</t>
+          <t>7,35; 9,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,0</t>
+          <t>5,73; 7,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,0</t>
+          <t>6,5; 7,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,85; 9,98</t>
+          <t>8,01; 10,23</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,73</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,64</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8,23</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,24</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,73</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,64</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,31</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,4</t>
+          <t>7,68; 10,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,02</t>
+          <t>7,27; 10,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 9,78</t>
+          <t>8,02; 10,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,2; 10,37</t>
+          <t>9,34; 14,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 10,25</t>
+          <t>7,33; 10,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 11,16</t>
+          <t>6,16; 7,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 10,82</t>
+          <t>7,08; 9,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 15,13</t>
+          <t>8,5; 10,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 9,71</t>
+          <t>7,76; 9,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,06</t>
+          <t>7,06; 9,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 9,71</t>
+          <t>7,8; 9,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 12,46</t>
+          <t>9,34; 12,29</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,41</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,19</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,11</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>9,03</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,15</t>
+          <t>5,82; 6,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,72</t>
+          <t>5,39; 6,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,64</t>
+          <t>5,91; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,97</t>
+          <t>8,66; 11,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 6,94</t>
+          <t>5,86; 7,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,61</t>
+          <t>4,77; 5,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,9; 6,98</t>
+          <t>5,65; 6,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,31</t>
+          <t>7,81; 9,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 6,81</t>
+          <t>5,96; 6,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 5,96</t>
+          <t>5,25; 6,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,65</t>
+          <t>5,89; 6,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,21; 9,77</t>
+          <t>8,42; 9,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5,24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,71</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,52</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.625441442554861</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.317969549440305</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.748228059581712</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.713348784171739</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.344053254367251</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.473234367412095</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>2.666048706046597</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>5.241537641112303</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>2.496184235208681</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.394062016697998</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2.705301679663943</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>4.52451543729138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 3,18</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,99; 2,92</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,25; 3,37</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,03; 4,63</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,05; 2,83</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,18; 2,89</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 3,23</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4,12; 7,1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2,24; 2,82</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2,17; 2,73</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2,39; 3,14</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,83; 5,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2.224901320047119</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.991382953380887</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2.252130624734023</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>3.029697392744984</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>2.053572879775705</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>2.179828401629095</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>2.22805016789742</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>4.118867144613989</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>2.235084210047885</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>2.16508720589161</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>2.387837387440427</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>3.831701177511827</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.179334402813683</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.919114975717853</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.369293645455461</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.626990612561415</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.828860240749028</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.891259733875373</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3.234405208398877</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>7.100447119843349</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2.82466184249064</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2.733864082873823</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>3.138142942121755</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>5.510578644637649</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,5</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,47</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,67</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,04</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,05</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4,83</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>8,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,45; 5,67</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,36; 5,75</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,88; 6,11</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7,33; 10,07</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,57; 5,92</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,05; 6,14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,41; 5,74</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6,68; 9,87</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4,64; 5,62</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4,37; 5,53</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4,91; 5,79</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,31; 9,31</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.996140619762448</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.965391414453391</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.499893307873242</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>8.472827921675185</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.104049367819376</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>4.668099448701012</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.040657906654167</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>7.749878826521038</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.051519124252899</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>4.82504688110597</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>5.293313436826931</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>8.104836992888231</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,06</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,93</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,41</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,38</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8,31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>8,23</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6,27</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7,16</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>8,92</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4.449306902969862</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4.362800378778461</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4.875123846897865</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>7.327945477250545</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>4.573833033027351</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4.047455062909288</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4.405999462766511</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>6.677006741652606</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>4.638232821025553</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>4.366324784578518</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>4.90714086035449</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>7.307632129613959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,96; 9,85</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5,99; 8,05</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,93; 8,32</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>8,23; 11,2</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,13; 11,22</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,06; 6,59</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,46; 8,5</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7,2; 10,77</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>7,35; 9,65</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>5,73; 7,07</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6,5; 7,96</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,01; 10,23</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.67497163652297</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.749543796302448</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.105698203121644</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.06600102291365</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.916144377102988</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>6.136868983190118</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.736842228289444</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>9.87052246469208</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5.617517710439277</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>5.525883644169479</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>5.786929563824075</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>9.309181971332638</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,73</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,64</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,47</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,23</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,46</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8,6</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8,75</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,37</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>8.061900640907162</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.776412338315001</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.927584508530246</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>9.516099001360805</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8.405899506618681</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>5.730401954781714</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>7.378649820299086</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>8.306273638235252</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>8.231406556479676</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>6.267774592858831</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>7.158276349238261</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>8.915676083992844</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7,68; 10,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,27; 10,94</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8,02; 10,81</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9,34; 14,37</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,33; 10,39</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 7,94</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,08; 9,78</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8,5; 10,63</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7,76; 9,68</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7,06; 9,13</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7,8; 9,83</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,34; 12,29</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.963629395924791</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>5.994229796536749</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.928943333042342</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>8.228241091480683</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>7.133549734300224</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5.064202501685141</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>6.455418631195212</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>7.201207714652374</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7.351647030931994</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>5.728458108997001</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>6.501697129557898</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>8.005888179282552</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.849394844222175</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.045146721802507</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.319936495038863</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>11.19954273843147</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>11.21726455911589</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>6.586182890230758</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>8.498390721718451</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>10.77369839925746</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>9.648211536024888</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>7.067312483717378</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>7.959822311534958</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>10.23472745159081</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>8.732216775119587</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>8.640069001816979</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>9.26008146164537</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>11.16131166151159</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>8.473425091677885</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>6.995568592136538</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>8.22775614642511</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>9.459984417371725</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>8.600771106748761</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>7.8336557621962</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>8.751624885039577</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>10.36663533595095</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7.680670529371179</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>7.266188248930021</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>8.016874428166204</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>9.338586825868768</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.328944448577576</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>6.159238500035089</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>7.082704460480458</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>8.5020064131624</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7.756868199596709</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>7.06408213810358</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>7.798908022719858</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>9.3390000275948</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.37515129934859</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.93968920889139</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.80834862737032</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>14.36662193041904</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>10.38757223861947</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.938264182063099</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>9.782366345637339</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>10.62512348956973</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>9.682372529399776</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>9.127445623414753</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>9.832680785094189</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>12.29277342189119</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,38</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,19</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8,4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6,26</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5,82; 6,89</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5,39; 6,64</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5,91; 6,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8,66; 11,12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,86; 7,04</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,77; 5,69</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,65; 6,67</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7,81; 9,31</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5,96; 6,81</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5,25; 6,01</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5,89; 6,62</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,42; 9,85</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>6.313500401941613</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.927250755169738</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>6.409716475155274</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>9.626501739644102</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>6.375251424384292</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5.187268300719906</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>6.112714209750386</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>8.398583892350468</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6.34440587214184</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>5.569766014913752</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>6.264766149745702</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.025558523926851</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>5.823207279982057</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5.387702943318156</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>5.910952614123493</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>8.657597770561066</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>5.861214706991507</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>4.770470046331008</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>5.650762711975142</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>7.808656220437176</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5.963507821291759</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>5.247565463430572</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>5.892573012397035</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>8.421109842676843</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.889023733518772</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.644418648348846</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.945046292950738</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>11.115460547874</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>7.043998315793036</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.687531049695793</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>6.669640298919225</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>9.311771362622764</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6.814682427607019</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>6.00897061354271</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>6.616622732066278</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>9.852484715821992</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
